--- a/AAII_Financials/Yearly/WRTBY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WRTBY_YR_FIN.xlsx
@@ -729,10 +729,10 @@
         <v>5438400</v>
       </c>
       <c r="I8" s="3">
-        <v>5657500</v>
+        <v>5634300</v>
       </c>
       <c r="J8" s="3">
-        <v>5824300</v>
+        <v>5804100</v>
       </c>
       <c r="K8" s="3">
         <v>5942300</v>
@@ -795,10 +795,10 @@
         <v>2378000</v>
       </c>
       <c r="I10" s="3">
-        <v>2409800</v>
+        <v>2386500</v>
       </c>
       <c r="J10" s="3">
-        <v>2608000</v>
+        <v>2587800</v>
       </c>
       <c r="K10" s="3">
         <v>2750200</v>
@@ -987,10 +987,10 @@
         <v>5120000</v>
       </c>
       <c r="I17" s="3">
-        <v>5370000</v>
+        <v>5346800</v>
       </c>
       <c r="J17" s="3">
-        <v>5423600</v>
+        <v>5403400</v>
       </c>
       <c r="K17" s="3">
         <v>5388100</v>
